--- a/artfynd/A 4528-2022 artfynd.xlsx
+++ b/artfynd/A 4528-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4528-2022 artfynd.xlsx
+++ b/artfynd/A 4528-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110258799</v>
+        <v>110258812</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580239.398964926</v>
+        <v>580090</v>
       </c>
       <c r="R2" t="n">
-        <v>7029911.604892788</v>
+        <v>7029961</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>110258804</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580228.5707785181</v>
+        <v>580228</v>
       </c>
       <c r="R3" t="n">
-        <v>7029895.635030583</v>
+        <v>7029895</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110258795</v>
+        <v>110258789</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580165.2144933185</v>
+        <v>580075</v>
       </c>
       <c r="R4" t="n">
-        <v>7029986.443872711</v>
+        <v>7030031</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,19 +937,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110258791</v>
+        <v>110258811</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580106.7869939405</v>
+        <v>580091</v>
       </c>
       <c r="R5" t="n">
-        <v>7030024.0021436</v>
+        <v>7029971</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,19 +1034,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110258805</v>
+        <v>110258791</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580154.7901967077</v>
+        <v>580107</v>
       </c>
       <c r="R6" t="n">
-        <v>7029954.338028162</v>
+        <v>7030024</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,19 +1131,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110258807</v>
+        <v>110258792</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580115.3706044954</v>
+        <v>580135</v>
       </c>
       <c r="R7" t="n">
-        <v>7029986.093253346</v>
+        <v>7030005</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,19 +1228,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110258813</v>
+        <v>110258793</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580078.632439226</v>
+        <v>580148</v>
       </c>
       <c r="R8" t="n">
-        <v>7029964.542333677</v>
+        <v>7030014</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,19 +1325,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110258812</v>
+        <v>110258794</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580089.5056305802</v>
+        <v>580167</v>
       </c>
       <c r="R9" t="n">
-        <v>7029960.777633974</v>
+        <v>7029981</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1532,19 +1422,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,58 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110258809</v>
+        <v>110258795</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västansjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580095.4194171287</v>
+        <v>580165</v>
       </c>
       <c r="R10" t="n">
-        <v>7029975.726693221</v>
+        <v>7029987</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1652,19 +1519,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,16 +1551,11 @@
         <v>110258796</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1731,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580176.9857170901</v>
+        <v>580177</v>
       </c>
       <c r="R11" t="n">
-        <v>7029946.820385816</v>
+        <v>7029947</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1764,19 +1616,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110258811</v>
+        <v>110258805</v>
       </c>
       <c r="B12" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1843,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580090.6054824741</v>
+        <v>580155</v>
       </c>
       <c r="R12" t="n">
-        <v>7029970.672567402</v>
+        <v>7029955</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1876,19 +1713,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110258789</v>
+        <v>110258807</v>
       </c>
       <c r="B13" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1955,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580074.7402229073</v>
+        <v>580116</v>
       </c>
       <c r="R13" t="n">
-        <v>7030030.376625738</v>
+        <v>7029986</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1988,19 +1810,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110258792</v>
+        <v>110258809</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,34 +1850,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västansjömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580135.0972819231</v>
+        <v>580096</v>
       </c>
       <c r="R14" t="n">
-        <v>7030005.424582954</v>
+        <v>7029976</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2100,19 +1915,9 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,50 +1944,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110258794</v>
+        <v>110258797</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västansjömyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580167.6046107237</v>
+        <v>580231</v>
       </c>
       <c r="R15" t="n">
-        <v>7029980.672995833</v>
+        <v>7029915</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2212,19 +2020,14 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,6 +2051,297 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>110258815</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Västansjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>580025</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7029960</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>110258799</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Västansjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>580239</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7029911</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110258813</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Västansjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>580079</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7029965</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4528-2022 artfynd.xlsx
+++ b/artfynd/A 4528-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258812</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258804</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258789</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258811</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258791</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258792</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258793</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258794</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258795</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258796</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258805</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258807</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258809</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2051,6 +2121,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258797</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2148,6 +2223,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258815</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2245,6 +2325,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258799</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2342,8 +2427,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110258813</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>